--- a/5/search/FY5_Missile1_results/solutions_direction_126.0.xlsx
+++ b/5/search/FY5_Missile1_results/solutions_direction_126.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
         <v>90</v>
       </c>
       <c r="B2" t="n">
-        <v>100.8</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
         <v>20</v>
@@ -502,7 +502,7 @@
         <v>13000</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
@@ -511,7 +511,7 @@
         <v>13000</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>1300</v>
@@ -522,106 +522,351 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99</v>
+        <v>94.5</v>
       </c>
       <c r="B3" t="n">
-        <v>92.40000000000001</v>
+        <v>118</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>12710.90910860565</v>
+        <v>12851.86922726583</v>
       </c>
       <c r="F3" t="n">
-        <v>-174.7519465801852</v>
+        <v>-117.8200739118545</v>
       </c>
       <c r="G3" t="n">
         <v>1300</v>
       </c>
       <c r="H3" t="n">
-        <v>12682.00001946622</v>
+        <v>12842.61105396994</v>
       </c>
       <c r="I3" t="n">
-        <v>7.7728587617963</v>
+        <v>-0.1838285313453838</v>
       </c>
       <c r="J3" t="n">
-        <v>1280.4</v>
+        <v>1295.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117</v>
+        <v>94.5</v>
       </c>
       <c r="B4" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="C4" t="n">
         <v>16</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12841.82646301267</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.785344805985915</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12841.82646301267</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9.785344805985915</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K4" t="n">
         <v>4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>12186.44902446673</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-403.3163086544448</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1300</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11983.06128058342</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-4.145385818056013</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1221.6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="B5" t="n">
-        <v>117.6</v>
+        <v>114</v>
       </c>
       <c r="C5" t="n">
         <v>16</v>
       </c>
       <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12714.66353576662</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-198.4564667544687</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12678.99647773745</v>
+      </c>
+      <c r="I5" t="n">
+        <v>26.73647490122272</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110</v>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12589.13615961361</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-288.628940100089</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12512.09918954116</v>
+      </c>
+      <c r="I6" t="n">
+        <v>32.25313363114424</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1255.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>114</v>
+      </c>
+      <c r="C7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12574.19565632683</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-226.3972651946378</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12520.97011336768</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-4.696923343967569</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1280.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>140</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12607.81178872208</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-366.4185337319032</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12509.7647359026</v>
+      </c>
+      <c r="I8" t="n">
+        <v>41.97683283512106</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1255.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B9" t="n">
+        <v>110</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12326.47715903744</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-373.9720227801354</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12158.0964487968</v>
+      </c>
+      <c r="I9" t="n">
+        <v>32.53497152483078</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1221.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>138</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12366.27623600341</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-470.0554941613093</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12155.03498133788</v>
+      </c>
+      <c r="I10" t="n">
+        <v>39.92600778492096</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1221.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>117</v>
+      </c>
+      <c r="B11" t="n">
+        <v>112</v>
+      </c>
+      <c r="C11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12186.44902446673</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-403.3163086544448</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H11" t="n">
+        <v>11983.06128058342</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-4.145385818056013</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1221.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126</v>
+      </c>
+      <c r="B12" t="n">
+        <v>118</v>
+      </c>
+      <c r="C12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
-        <v>11894.02326928648</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-477.753623384099</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="H5" t="n">
-        <v>11548.40554093851</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-2.051630691629953</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="E12" t="n">
+        <v>11890.26144367181</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-472.5759146200992</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11543.46814481925</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.744112061119836</v>
+      </c>
+      <c r="J12" t="n">
         <v>1177.5</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K12" t="n">
         <v>2</v>
       </c>
     </row>
